--- a/Insurance Rate Data Scraper/output/nm_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/nm_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U132"/>
+  <dimension ref="A1:U133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,7 +622,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -723,7 +722,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -819,7 +817,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -920,7 +917,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1021,7 +1017,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1122,7 +1117,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1223,7 +1217,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1324,7 +1317,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1425,7 +1417,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1526,7 +1517,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1627,7 +1617,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1728,7 +1717,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3299,7 +3287,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3715,7 +3702,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3816,7 +3802,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3917,7 +3902,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4018,7 +4002,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4119,7 +4102,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4220,7 +4202,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4321,7 +4302,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4422,7 +4402,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5258,7 +5237,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5359,7 +5337,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5460,7 +5437,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5561,7 +5537,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5662,7 +5637,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5763,7 +5737,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5864,7 +5837,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5965,7 +5937,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6066,7 +6037,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6167,7 +6137,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6268,7 +6237,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6369,7 +6337,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6470,7 +6437,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6571,7 +6537,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6672,7 +6637,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6773,7 +6737,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -7399,7 +7362,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7500,7 +7462,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7916,7 +7877,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -8017,7 +7977,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -8118,7 +8077,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -8219,7 +8177,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -8320,7 +8277,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -8631,7 +8587,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -8732,7 +8687,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -8833,7 +8787,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -8934,7 +8887,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -9035,7 +8987,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -9136,7 +9087,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -9237,7 +9187,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -9338,7 +9287,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -10804,7 +10752,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -10905,7 +10852,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -11006,7 +10952,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -11317,7 +11262,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -11418,7 +11362,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -11514,7 +11457,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -11610,7 +11552,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -11706,7 +11647,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -11807,7 +11747,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -11908,7 +11847,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -12004,7 +11942,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -12100,7 +12037,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -13711,7 +13647,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -13812,7 +13747,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -13911,6 +13845,103 @@
       <c r="U132" t="inlineStr">
         <is>
           <t>direct</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>NM</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Allstate North American Insurance Company</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>4.100%</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>-1.100%</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>ALSE-134500230</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>File &amp; Use With Review</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>output/pdfs/NM/134500230/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
     </row>

--- a/Insurance Rate Data Scraper/output/nm_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/nm_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U148"/>
+  <dimension ref="A1:U171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15261,6 +15261,2169 @@
         </is>
       </c>
       <c r="U148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>NM</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>10/02/2026</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I149" t="n">
+        <v>10906</v>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>19717622</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>21.620%</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>-17.260%</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>SFMA-134828655</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>File &amp; Use With Review</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>output/pdfs/NM/134828655/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>NM</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>10/02/2026</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I150" t="n">
+        <v>448380</v>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>482860505</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>18.450%</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>-17.440%</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>SFMA-134828655</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>File &amp; Use With Review</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>output/pdfs/NM/134828655/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>NM</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>08/01/2026</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>3.000%</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>648110</t>
+        </is>
+      </c>
+      <c r="I151" t="n">
+        <v>14511</v>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>21886874</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>-3.300%</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>8.600%</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>SFMA-134996673</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>File &amp; Use With Review</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>output/pdfs/NM/134996673/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>NM</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>08/01/2026</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>-2.000%</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>-9714189</t>
+        </is>
+      </c>
+      <c r="I152" t="n">
+        <v>515403</v>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>479112866</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>-13.300%</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>11.300%</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>SFMA-134996673</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>File &amp; Use With Review</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>output/pdfs/NM/134996673/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>NM</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>05/14/2026</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>GEICO Casualty Company</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I153" t="n">
+        <v>8764</v>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>11101978</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>12.400%</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>-10.900%</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>GECC-134944719</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>File &amp; Use With Review</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>output/pdfs/NM/134944719/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>NM</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>05/14/2026</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>GEICO Marine Insurance Company</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I154" t="n">
+        <v>1852</v>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>2370928</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>17.800%</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>-19.000%</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>GECC-134944719</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>File &amp; Use With Review</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>output/pdfs/NM/134944719/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>NM</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Allstate Fire and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I155" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>97353542</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>ALSE-134916786</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>File &amp; Use With Review</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>output/pdfs/NM/134916786/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>NM</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>08/18/2026</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Allstate North American Insurance Company</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>04.0003 Owner Occupied Homeowners</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I156" t="n">
+        <v>8743</v>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>17705157</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>5.000%</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>-3.700%</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>ALSE-135044132</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>File &amp; Use With Review</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>output/pdfs/NM/135044132/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>NM</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Allstate North American Insurance Company</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>-1.100%</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>-248706</t>
+        </is>
+      </c>
+      <c r="I157" t="n">
+        <v>8327</v>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>22609626</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>ALSE-134921864</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>File &amp; Use With Review</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>output/pdfs/NM/134921864/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>NM</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>05/21/2026</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Allstate North American Insurance Company</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>04.0004 Tenant Homeowners</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I158" t="n">
+        <v>1149</v>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>231368</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>3.100%</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>-1.300%</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>ALSE-134930983</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>File &amp; Use With Review</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>output/pdfs/NM/134930983/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>NM</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>08/17/2026</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I159" t="n">
+        <v>0</v>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>LBPM-135002829</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>File &amp; Use With Review</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>output/pdfs/NM/135002829/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>NM</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>08/17/2026</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I160" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>LBPM-135002829</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>File &amp; Use With Review</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>output/pdfs/NM/135002829/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>NM</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>08/29/2026</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>0.500%</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>-0.020%</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>-4570</t>
+        </is>
+      </c>
+      <c r="I161" t="n">
+        <v>8331</v>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>23112626</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>7.000%</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>-3.540%</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>LBPM-134993021</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>File &amp; Use With Review</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>output/pdfs/NM/134993021/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>NM</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>08/15/2026</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>04.0004 Tenant Homeowners</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>-0.400%</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>-1796</t>
+        </is>
+      </c>
+      <c r="I162" t="n">
+        <v>1225</v>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>427607</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>-40.000%</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>LBPM-135017330</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>File &amp; Use With Review</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>output/pdfs/NM/135017330/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>NM</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>10/26/2026</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Encompass Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>17.200%</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>17.200%</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>138882</t>
+        </is>
+      </c>
+      <c r="I163" t="n">
+        <v>267</v>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>807451</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>33.300%</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>6.000%</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>GMMX-135019110</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>File &amp; Use With Review</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>output/pdfs/NM/135019110/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>NM</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>04/26/2026</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Farmers Insurance Exchange</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>-11.700%</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>-1984</t>
+        </is>
+      </c>
+      <c r="I164" t="n">
+        <v>12238</v>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>26916404</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>17.300%</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>-14.000%</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>FARM-134895757</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>File &amp; Use With Review</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>output/pdfs/NM/134895757/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>NM</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>08/11/2026</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Farmers Insurance Company of Arizona</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>3.000%</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>3.000%</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>2391186</t>
+        </is>
+      </c>
+      <c r="I165" t="n">
+        <v>30744</v>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>79141009</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>14.100%</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>-14.000%</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>FARM-135026312</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>output/pdfs/NM/135026312/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>NM</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>08/11/2026</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Farmers Insurance Exchange</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>3.000%</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>3.000%</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>813518</t>
+        </is>
+      </c>
+      <c r="I166" t="n">
+        <v>13418</v>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>26916404</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>26.500%</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>-12.900%</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>FARM-135026312</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>output/pdfs/NM/135026312/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>NM</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>07/27/2026</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Fire Insurance Exchange</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I167" t="n">
+        <v>18379</v>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>27789260</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>FARM-135026184</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>File &amp; Use With Review</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>output/pdfs/NM/135026184/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>NM</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>12/11/2026</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Garrison Property and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I168" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>30721070</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>USAA-134970368</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>File &amp; Use With Review</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>output/pdfs/NM/134975405/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>NM</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>12/11/2026</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>USAA Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I169" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>53405571</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>USAA-134970368</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>File &amp; Use With Review</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>output/pdfs/NM/134975405/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>NM</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>12/11/2026</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>USAA General Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>48670830</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>USAA-134970368</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>File &amp; Use With Review</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>output/pdfs/NM/134975405/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>NM</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>12/11/2026</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>United Services Automobile Association</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I171" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>61051246</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>USAA-134970368</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>File &amp; Use With Review</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>output/pdfs/NM/134975405/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
